--- a/Excel/MonsterModelConfig.xlsx
+++ b/Excel/MonsterModelConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -1046,7 +1046,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
@@ -1097,7 +1097,7 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:16">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:16">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1135,7 +1135,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:16">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:16">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -1173,7 +1173,7 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:16">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:16">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -1211,7 +1211,7 @@
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="3:12">
+    <row r="6" ht="24" customHeight="1" spans="1:16">
       <c r="C6">
         <v>1</v>
       </c>
@@ -1228,18 +1228,18 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I6">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J6">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="K6"/>
       <c r="L6"/>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="3:12">
+    <row r="7" ht="24" customHeight="1" spans="1:16">
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7"/>
@@ -1251,7 +1251,7 @@
       <c r="K7"/>
       <c r="L7"/>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="3:12">
+    <row r="8" ht="24" customHeight="1" spans="1:16">
       <c r="C8"/>
       <c r="D8"/>
       <c r="E8"/>
@@ -1263,7 +1263,7 @@
       <c r="K8"/>
       <c r="L8"/>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="3:12">
+    <row r="9" ht="24" customHeight="1" spans="1:16">
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9"/>
@@ -1275,7 +1275,7 @@
       <c r="K9"/>
       <c r="L9"/>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="3:12">
+    <row r="10" ht="24" customHeight="1" spans="1:16">
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
@@ -1287,7 +1287,7 @@
       <c r="K10"/>
       <c r="L10"/>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="3:12">
+    <row r="11" ht="24" customHeight="1" spans="1:16">
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11"/>
@@ -1299,7 +1299,7 @@
       <c r="K11"/>
       <c r="L11"/>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="3:12">
+    <row r="12" ht="24" customHeight="1" spans="1:16">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -1311,7 +1311,7 @@
       <c r="K12"/>
       <c r="L12"/>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="3:12">
+    <row r="13" ht="24" customHeight="1" spans="1:16">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -1323,7 +1323,7 @@
       <c r="K13"/>
       <c r="L13"/>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="3:12">
+    <row r="14" ht="24" customHeight="1" spans="1:16">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -1335,7 +1335,7 @@
       <c r="K14"/>
       <c r="L14"/>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="3:12">
+    <row r="15" ht="24" customHeight="1" spans="1:16">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -1347,7 +1347,7 @@
       <c r="K15"/>
       <c r="L15"/>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="3:12">
+    <row r="16" ht="24" customHeight="1" spans="1:16">
       <c r="C16"/>
       <c r="D16"/>
       <c r="E16"/>
@@ -1527,7 +1527,7 @@
       <c r="K30"/>
       <c r="L30"/>
     </row>
-    <row r="31" ht="24" customHeight="1" spans="3:11">
+    <row r="31" ht="24" customHeight="1" spans="3:12">
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
@@ -1550,7 +1550,7 @@
       <c r="K32"/>
       <c r="L32" s="5"/>
     </row>
-    <row r="33" ht="24" customHeight="1" spans="3:11">
+    <row r="33" ht="24" customHeight="1" spans="3:12">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1803,7 +1803,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 H3 I3 J3 K3 L3 E4 F4 H4 I4 J4 K4 L4 E5 F5 G5 H5 I5 J5 K5 L5 C3:C5 D4:D5 G3:G4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -1816,7 +1816,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
@@ -1834,7 +1834,7 @@
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" spans="1:15">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="E1" s="2"/>
@@ -1848,7 +1848,7 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
+    <row r="2" s="1" customFormat="1" spans="1:15">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="E2" s="2"/>
@@ -1862,7 +1862,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:15">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1886,7 +1886,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:12">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -1910,7 +1910,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:12">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:15">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -1944,7 +1944,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="7" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7"/>
@@ -1953,7 +1953,7 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="8" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C8"/>
       <c r="D8"/>
       <c r="E8"/>
@@ -1962,7 +1962,7 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="9" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9"/>
@@ -1971,7 +1971,7 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="10" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
@@ -1980,7 +1980,7 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="11" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11"/>
@@ -1989,7 +1989,7 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="12" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -1998,7 +1998,7 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="13" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -2007,7 +2007,7 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="14" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -2016,7 +2016,7 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="15" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -2025,7 +2025,7 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="16" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C16"/>
       <c r="D16"/>
       <c r="E16"/>
@@ -2234,7 +2234,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3:G3 E4 F4 G4 E5 F5 G5 C3:C5 D4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
